--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-27_yatay_yayginlastirma_ve_tekrar_onleme_uygulama_kaydi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-27_yatay_yayginlastirma_ve_tekrar_onleme_uygulama_kaydi.xlsx
@@ -804,7 +804,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-27&amp;C&amp;"Arial,Regular"&amp;11Yatay Yaygınlaştırma ve Tekrar Önleme Uygulama Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e5038a8962a4628"/>
   <x:tableParts count="1">
@@ -1156,7 +1157,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-27&amp;C&amp;"Arial,Regular"&amp;11Yatay Yaygınlaştırma ve Tekrar Önleme Uygulama Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R837dc7b2d7f7488c"/>
   <x:tableParts count="1">
@@ -1484,7 +1486,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-27&amp;C&amp;"Arial,Regular"&amp;11Yatay Yaygınlaştırma ve Tekrar Önleme Uygulama Kaydı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra763e87637234bb0"/>
   <x:tableParts count="1">
